--- a/assets/excel/biostride.xlsx
+++ b/assets/excel/biostride.xlsx
@@ -1499,26 +1499,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ph</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>buffer_ph</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>final_sample_ph</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ph_measurement_temperature</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ph_measurement_method</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ph_stability_notes</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ionic_strength</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>components</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>additives</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>description</t>
         </is>

--- a/assets/excel/biostride.xlsx
+++ b/assets/excel/biostride.xlsx
@@ -7,36 +7,49 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dataset" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Study" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sample" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="SamplePreparation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Instrument" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="CryoEMInstrument" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="XRayInstrument" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="SAXSInstrument" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ExperimentRun" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="WorkflowRun" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="DataFile" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Image" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Image2D" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Image3D" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="FTIRImage" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="FluorescenceImage" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="OpticalImage" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="XRFImage" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="ImageFeature" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="OntologyTerm" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="MolecularComposition" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="BufferComposition" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="StorageConditions" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="CryoEMPreparation" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="XRayPreparation" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="SAXSPreparation" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="ExperimentalConditions" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="DataCollectionStrategy" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="QualityMetrics" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="ComputeResources" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="ProteinAnnotation" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FunctionalSite" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="StructuralFeature" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="LigandInteraction" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ProteinProteinInteraction" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="MutationEffect" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="BiophysicalProperty" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="ConformationalEnsemble" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="ConformationalState" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="PostTranslationalModification" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="DatabaseCrossReference" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="EvolutionaryConservation" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="AggregatedProteinView" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Dataset" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Study" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Sample" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="SamplePreparation" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Instrument" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="CryoEMInstrument" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="XRayInstrument" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="SAXSInstrument" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="ExperimentRun" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="WorkflowRun" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="DataFile" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Image" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Image2D" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Image3D" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="FTIRImage" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="FluorescenceImage" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="OpticalImage" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="XRFImage" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="ImageFeature" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="OntologyTerm" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="MolecularComposition" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="BufferComposition" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="StorageConditions" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="CryoEMPreparation" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="XRayPreparation" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="SAXSPreparation" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="ExperimentalConditions" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="DataCollectionStrategy" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="QualityMetrics" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet name="ComputeResources" sheetId="43" state="visible" r:id="rId43"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,6 +455,494 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>protein_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pdb_entry</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>chain_id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>residue_range</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>confidence_score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>evidence_type</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>evidence_code</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>source_database</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>annotation_method</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>publication_ids</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"experimental,predicted,inferred,literature,author_statement,curator_inference"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>modification_type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>modified_residue</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>modification_group</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>mass_shift</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>functional_effect</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>regulatory_role</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>enzyme</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>removal_enzyme</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>protein_id</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>pdb_entry</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>chain_id</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>residue_range</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>confidence_score</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>evidence_type</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>evidence_code</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>source_database</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>annotation_method</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>publication_ids</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"phosphorylation,acetylation,methylation,ubiquitination,sumoylation,glycosylation,palmitoylation,myristoylation,prenylation,nitrosylation,oxidation,hydroxylation,proteolysis,deamidation,adp_ribosylation"</formula1>
+    </dataValidation>
+    <dataValidation sqref="N2:N1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"experimental,predicted,inferred,literature,author_statement,curator_inference"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>database_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>database_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>database_url</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>last_updated</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"uniprot,pdb,pfam,cath,scop,interpro,chembl,chebi,pubchem,drugbank,omim,clinvar,cosmic,gnomad,intact,string,biogrid,reactome,kegg,go"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>conservation_score</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>conserved_residues</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>variable_residues</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>conservation_method</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>alignment_depth</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>taxonomic_range</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>coevolved_residues</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>protein_id</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pdb_entry</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>chain_id</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>residue_range</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>confidence_score</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>evidence_type</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>evidence_code</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>source_database</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>annotation_method</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>publication_ids</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="M2:M1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"experimental,predicted,inferred,literature,author_statement,curator_inference"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>uniprot_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>protein_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>organism</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>organism_id</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pdb_entries</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>functional_sites</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>structural_features</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>protein_interactions</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ligand_interactions</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>mutations</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ptms</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>biophysical_properties</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>conformational_ensemble</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>evolutionary_conservation</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>cross_references</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -482,7 +983,883 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>samples</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>sample_preparations</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>instrument_runs</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>workflow_runs</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>data_files</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>images</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>aggregated_protein_views</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AB1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>sample_code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>sample_type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>molecular_composition</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>molecular_weight</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>concentration</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>concentration_unit</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>buffer_composition</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>preparation_method</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>storage_conditions</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>organism</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>anatomy</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>cell_type</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>parent_sample_id</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>purity_percentage</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>quality_metrics</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>functional_sites</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>structural_features</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>protein_interactions</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ligand_interactions</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>mutation_effects</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>ptm_annotations</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>biophysical_properties</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>evolutionary_conservation</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>conformational_ensemble</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>database_cross_references</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"protein,nucleic_acid,complex,membrane_protein,virus,organelle"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"mg_per_ml,micromolar,millimolar,nanomolar"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>preparation_type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>sample_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>preparation_date</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>operator_id</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>protocol_description</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"cryo_em,xray_crystallography,saxs,sans,protein_expression,protein_purification,negative_stain"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>instrument_code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>manufacturer</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>installation_date</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>current_status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"operational,maintenance,offline,commissioning"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>accelerating_voltage</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>cs_corrector</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>phase_plate</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>detector_type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>detector_dimensions</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pixel_size_min</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pixel_size_max</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>autoloader_capacity</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>instrument_code</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>manufacturer</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>installation_date</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>current_status</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"direct_electron,ccd,cmos,hybrid_pixel"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"operational,maintenance,offline,commissioning"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>site_type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>site_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>residues</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ligand_interactions</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>conservation_score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>functional_importance</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>go_terms</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ec_number</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>protein_id</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>pdb_entry</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>chain_id</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>residue_range</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>confidence_score</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>evidence_type</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>evidence_code</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>source_database</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>annotation_method</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>publication_ids</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="N2:N1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"experimental,predicted,inferred,literature,author_statement,curator_inference"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>source_type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>energy_min</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>energy_max</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>beam_size_min</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>beam_size_max</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>flux_density</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>monochromator_type</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>goniometer_type</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>crystal_cooling_capability</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>instrument_code</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>manufacturer</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>installation_date</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>current_status</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"synchrotron,rotating_anode,microfocus,metal_jet"</formula1>
+    </dataValidation>
+    <dataValidation sqref="N2:N1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"operational,maintenance,offline,commissioning"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>q_range_min</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>q_range_max</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>detector_distance_min</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>detector_distance_max</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sample_changer_capacity</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>temperature_control_range</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>instrument_code</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>manufacturer</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>installation_date</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>current_status</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="K2:K1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"operational,maintenance,offline,commissioning"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>experiment_code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>sample_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>instrument_id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>experiment_date</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>operator_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>technique</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>experimental_conditions</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>data_collection_strategy</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>quality_metrics</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>raw_data_location</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>processing_status</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"cryo_em,xray_crystallography,saxs,waxs,sans,cryo_et,electron_microscopy,mass_spectrometry"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"raw,preprocessing,processing,completed,failed"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -573,7 +1950,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -647,7 +2024,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -713,7 +2090,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -789,7 +2166,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -870,7 +2247,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -971,7 +2348,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1092,7 +2469,147 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>feature_type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>secondary_structure</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>solvent_accessibility</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>backbone_flexibility</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>disorder_probability</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>conformational_state</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>structural_motif</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>domain_assignment</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>domain_id</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>protein_id</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>pdb_entry</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>chain_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>residue_range</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>confidence_score</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>evidence_type</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>evidence_code</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>source_database</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>annotation_method</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>publication_ids</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="4">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"alpha_helix,beta_sheet,beta_strand,turn,coil,disordered_region,transmembrane_helix,signal_peptide,transit_peptide,domain,repeat,zinc_finger,coiled_coil,motif,cavity,channel,pore,hinge,linker"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"helix,sheet,turn,coil,helix_310,helix_pi,bend,bridge"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"open,closed,intermediate,active,inactive,apo,holo,substrate_bound,product_bound,inhibitor_bound,partially_open,partially_closed"</formula1>
+    </dataValidation>
+    <dataValidation sqref="O2:O1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"experimental,predicted,inferred,literature,author_statement,curator_inference"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1203,7 +2720,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1324,7 +2841,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1350,114 +2867,53 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>samples</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>sample_preparations</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>instrument_runs</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>workflow_runs</t>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>definition</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ontology</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>id</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>data_files</t>
+          <t>title</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>images</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>label</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>definition</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ontology</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1493,7 +2949,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1529,7 +2985,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1575,7 +3031,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1649,7 +3105,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1710,7 +3166,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1756,7 +3212,99 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ligand_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ligand_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ligand_smiles</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>binding_affinity</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>binding_affinity_type</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>binding_affinity_unit</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>interaction_type</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>binding_site_residues</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>is_cofactor</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>is_drug_like</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>druggability_score</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>interaction_distance</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kd,ki,ic50,ec50,ka,km"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"molar,millimolar,micromolar,nanomolar,picomolar"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"covalent,hydrogen_bond,ionic,van_der_waals,hydrophobic,aromatic,pi_stacking,cation_pi,metal_coordination,disulfide"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1807,7 +3355,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1858,7 +3406,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1909,478 +3457,393 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:R1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>sample_code</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>sample_type</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>molecular_composition</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>molecular_weight</t>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cpu_hours</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>gpu_hours</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>memory_gb</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>storage_gb</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>concentration</t>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>partner_protein_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>partner_chain_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>interface_residues</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>partner_interface_residues</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>interface_area</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>concentration_unit</t>
+          <t>binding_energy</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>buffer_composition</t>
+          <t>dissociation_constant</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>preparation_method</t>
+          <t>complex_stability</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>storage_conditions</t>
+          <t>biological_assembly</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>organism</t>
+          <t>interaction_evidence</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>anatomy</t>
+          <t>protein_id</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>cell_type</t>
+          <t>pdb_entry</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>parent_sample_id</t>
+          <t>chain_id</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>purity_percentage</t>
+          <t>residue_range</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>quality_metrics</t>
+          <t>confidence_score</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>evidence_type</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>evidence_code</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>source_database</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>annotation_method</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>publication_ids</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
           <t>id</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="H2:H1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"stable,transient,weak,strong,obligate,non_obligate"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"experimental,predicted,homology,coexpression,colocalization,genetic,physical,functional"</formula1>
+    </dataValidation>
+    <dataValidation sqref="P2:P1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"experimental,predicted,inferred,literature,author_statement,curator_inference"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>mutation_type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>effect_on_stability</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>delta_delta_g</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>effect_on_function</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>functional_impact_description</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>disease_association</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>omim_id</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>clinical_significance</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>allele_frequency</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>protein_id</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>pdb_entry</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>chain_id</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>residue_range</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>confidence_score</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>evidence_type</t>
+        </is>
+      </c>
       <c r="Q1" t="inlineStr">
         <is>
+          <t>evidence_code</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>source_database</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>annotation_method</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>publication_ids</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>title</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="5">
     <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"protein,nucleic_acid,complex,membrane_protein,virus,organelle"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"mg_per_ml,micromolar,millimolar,nanomolar"</formula1>
+      <formula1>"missense,nonsense,frameshift,deletion,insertion,duplication,substitution"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"stabilizing,destabilizing,neutral,highly_stabilizing,highly_destabilizing"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"loss_of_function,gain_of_function,altered_function,no_effect,partial_loss,enhanced_function"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"pathogenic,likely_pathogenic,benign,likely_benign,uncertain_significance"</formula1>
+    </dataValidation>
+    <dataValidation sqref="P2:P1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"experimental,predicted,inferred,literature,author_statement,curator_inference"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>cpu_hours</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>gpu_hours</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>memory_gb</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>storage_gb</t>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>property_type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>preparation_type</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>sample_id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>preparation_date</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>operator_id</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>protocol_description</t>
+          <t>measurement_conditions</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>temperature</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>ph</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"cryo_em,xray_crystallography,saxs,sans,protein_expression,protein_purification,negative_stain"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>instrument_code</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>manufacturer</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>installation_date</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>current_status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"operational,maintenance,offline,commissioning"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:P1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>accelerating_voltage</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>cs_corrector</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>phase_plate</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>detector_type</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>detector_dimensions</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>pixel_size_min</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>pixel_size_max</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>autoloader_capacity</t>
+          <t>ionic_strength</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>instrument_code</t>
+          <t>experimental_method</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
-        <is>
-          <t>manufacturer</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>installation_date</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>current_status</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"direct_electron,ccd,cmos,hybrid_pixel"</formula1>
-    </dataValidation>
-    <dataValidation sqref="M2:M1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"operational,maintenance,offline,commissioning"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>source_type</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>energy_min</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>energy_max</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>beam_size_min</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>beam_size_max</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>flux_density</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>monochromator_type</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>goniometer_type</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>crystal_cooling_capability</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>instrument_code</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>manufacturer</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>installation_date</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>current_status</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -2389,10 +3852,10 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"synchrotron,rotating_anode,microfocus,metal_jet"</formula1>
-    </dataValidation>
-    <dataValidation sqref="N2:N1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"operational,maintenance,offline,commissioning"</formula1>
+      <formula1>"melting_temperature,stability,folding_rate,unfolding_rate,aggregation_propensity,solubility,hydrophobicity,isoelectric_point,extinction_coefficient,molecular_weight,diffusion_coefficient,sedimentation_coefficient,radius_of_gyration,hydrodynamic_radius"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"differential_scanning_calorimetry,isothermal_titration_calorimetry,circular_dichroism,fluorescence_spectroscopy,surface_plasmon_resonance,dynamic_light_scattering,analytical_ultracentrifugation,nuclear_magnetic_resonance,mass_spectrometry"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2405,87 +3868,62 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>q_range_min</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>q_range_max</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>detector_distance_min</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>detector_distance_max</t>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>protein_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>conformational_states</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>clustering_method</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>rmsd_threshold</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>sample_changer_capacity</t>
+          <t>transition_pathways</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>temperature_control_range</t>
+          <t>energy_landscape</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>instrument_code</t>
+          <t>principal_motions</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>manufacturer</t>
+          <t>id</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>title</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>installation_date</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>current_status</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="K2:K1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"operational,maintenance,offline,commissioning"</formula1>
-    </dataValidation>
-  </dataValidations>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2496,90 +3934,52 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>experiment_code</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>sample_id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>instrument_id</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>experiment_date</t>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>state_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>state_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pdb_entries</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>population</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>operator_id</t>
+          <t>free_energy</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>technique</t>
+          <t>rmsd_from_reference</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>experimental_conditions</t>
+          <t>characteristic_features</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>data_collection_strategy</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>quality_metrics</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>raw_data_location</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>processing_status</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"cryo_em,xray_crystallography,saxs,waxs,sans,cryo_et,electron_microscopy,mass_spectrometry"</formula1>
-    </dataValidation>
-    <dataValidation sqref="K2:K1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"raw,preprocessing,processing,completed,failed"</formula1>
-    </dataValidation>
-  </dataValidations>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/assets/excel/biostride.xlsx
+++ b/assets/excel/biostride.xlsx
@@ -2593,13 +2593,13 @@
   </sheetData>
   <dataValidations count="4">
     <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"alpha_helix,beta_sheet,beta_strand,turn,coil,disordered_region,transmembrane_helix,signal_peptide,transit_peptide,domain,repeat,zinc_finger,coiled_coil,motif,cavity,channel,pore,hinge,linker"</formula1>
+      <formula1>"alpha_helix,beta_sheet,beta_strand,turn,coil,disordered_region,transmembrane_helix,signal_peptide,transit_peptide,domain,repeat,zinc_finger,zinc_binding,coiled_coil,motif,cavity,channel,pore,hinge,linker"</formula1>
     </dataValidation>
     <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"helix,sheet,turn,coil,helix_310,helix_pi,bend,bridge"</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"open,closed,intermediate,active,inactive,apo,holo,substrate_bound,product_bound,inhibitor_bound,partially_open,partially_closed"</formula1>
+      <formula1>"open,closed,intermediate,active,inactive,apo,holo,substrate_bound,product_bound,inhibitor_bound,partially_open,partially_closed,disordered"</formula1>
     </dataValidation>
     <dataValidation sqref="O2:O1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"experimental,predicted,inferred,literature,author_statement,curator_inference"</formula1>

--- a/assets/excel/biostride.xlsx
+++ b/assets/excel/biostride.xlsx
@@ -23,33 +23,34 @@
     <sheet name="Dataset" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="Study" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="Sample" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="SamplePreparation" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Instrument" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="CryoEMInstrument" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="XRayInstrument" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="SAXSInstrument" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="ExperimentRun" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="WorkflowRun" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="DataFile" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Image" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Image2D" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Image3D" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="FTIRImage" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="FluorescenceImage" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="OpticalImage" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="XRFImage" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="ImageFeature" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="OntologyTerm" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="MolecularComposition" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="BufferComposition" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="StorageConditions" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet name="CryoEMPreparation" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet name="XRayPreparation" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet name="SAXSPreparation" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet name="ExperimentalConditions" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet name="DataCollectionStrategy" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet name="QualityMetrics" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet name="ComputeResources" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet name="ProteinConstruct" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="SamplePreparation" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Instrument" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="CryoEMInstrument" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="XRayInstrument" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="SAXSInstrument" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="ExperimentRun" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="WorkflowRun" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="DataFile" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Image" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Image2D" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Image3D" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="FTIRImage" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="FluorescenceImage" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="OpticalImage" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="XRFImage" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="ImageFeature" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="OntologyTerm" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="MolecularComposition" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="BufferComposition" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="StorageConditions" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="CryoEMPreparation" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="XRayPreparation" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="SAXSPreparation" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="ExperimentalConditions" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="DataCollectionStrategy" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet name="QualityMetrics" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet name="ComputeResources" sheetId="44" state="visible" r:id="rId44"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -989,56 +990,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>protein_constructs</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>samples</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>sample_preparations</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>instrument_runs</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>workflow_runs</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>data_files</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>aggregated_protein_views</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -1219,57 +1225,132 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:X1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>preparation_type</t>
+          <t>construct_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>sample_id</t>
+          <t>uniprot_id</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>preparation_date</t>
+          <t>gene_name</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>operator_id</t>
+          <t>ncbi_taxid</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>protocol_description</t>
+          <t>sequence_length_aa</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>construct_description</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>gene_synthesis_provider</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>codon_optimization_organism</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>vector_backbone</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>vector_name</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>promoter</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>tag_nterm</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>tag_cterm</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>cleavage_site</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>signal_peptide</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>selectable_marker</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>cloning_method</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>insert_boundaries</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>sequence_file_path</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>sequence_verified_by</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>verification_notes</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>id</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"cryo_em,xray_crystallography,saxs,sans,protein_expression,protein_purification,negative_stain"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1280,55 +1361,246 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:AS1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>instrument_code</t>
+          <t>preparation_type</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>manufacturer</t>
+          <t>sample_id</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>preparation_date</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>installation_date</t>
+          <t>operator_id</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>current_status</t>
+          <t>protocol_description</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>expression_system</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>host_strain_or_cell_line</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>culture_volume_l</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>antibiotic_selection</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>growth_temperature_c</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>induction_agent</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>inducer_concentration</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>induction_temperature_c</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>induction_time_h</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>od600_at_induction</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>harvest_timepoint</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>lysis_method</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>protease_inhibitors</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>purification_steps</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>affinity_type</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>affinity_column</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>lysis_buffer</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>wash_buffer</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>elution_buffer</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>tag_removal</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>protease</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>protease_ratio</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>cleavage_time_h</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>cleavage_temperature_c</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>second_affinity_reverse</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>iex_column</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>hic_column</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>sec_column</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>sec_buffer</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>concentration_method</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>final_buffer</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>final_concentration_mg_per_ml</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>yield_mg</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>purity_by_sds_page_percent</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>aggregation_assessment</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>aliquoting</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
           <t>id</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"operational,maintenance,offline,commissioning"</formula1>
+  <dataValidations count="3">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"cryo_em,xray_crystallography,saxs,sans,protein_expression,protein_purification,negative_stain"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"bacteria,yeast,insect,mammalian,cell_free"</formula1>
+    </dataValidation>
+    <dataValidation sqref="T2:T1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"affinity_ni_nta,affinity_co_nta,affinity_strep,affinity_mbp,affinity_gst,tag_cleavage,ion_exchange,hydrophobic_interaction,size_exclusion,dialysis"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1341,97 +1613,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>accelerating_voltage</t>
+          <t>instrument_code</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>cs_corrector</t>
+          <t>manufacturer</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>phase_plate</t>
+          <t>model</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>detector_type</t>
+          <t>installation_date</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>detector_dimensions</t>
+          <t>current_status</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>pixel_size_min</t>
+          <t>id</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>pixel_size_max</t>
+          <t>title</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
-        <is>
-          <t>autoloader_capacity</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>instrument_code</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>manufacturer</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>installation_date</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>current_status</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"direct_electron,ccd,cmos,hybrid_pixel"</formula1>
-    </dataValidation>
-    <dataValidation sqref="M2:M1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="1">
+    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"operational,maintenance,offline,commissioning"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1571,91 +1800,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>source_type</t>
+          <t>accelerating_voltage</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>energy_min</t>
+          <t>cs_corrector</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>energy_max</t>
+          <t>phase_plate</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>beam_size_min</t>
+          <t>detector_type</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>beam_size_max</t>
+          <t>detector_dimensions</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>flux_density</t>
+          <t>pixel_size_min</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>monochromator_type</t>
+          <t>pixel_size_max</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>goniometer_type</t>
+          <t>autoloader_capacity</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>crystal_cooling_capability</t>
+          <t>instrument_code</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>instrument_code</t>
+          <t>manufacturer</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>manufacturer</t>
+          <t>model</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>installation_date</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>installation_date</t>
+          <t>current_status</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>current_status</t>
+          <t>id</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>title</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -1663,10 +1887,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"synchrotron,rotating_anode,microfocus,metal_jet"</formula1>
-    </dataValidation>
-    <dataValidation sqref="N2:N1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"direct_electron,ccd,cmos,hybrid_pixel"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"operational,maintenance,offline,commissioning"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1680,84 +1904,102 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>q_range_min</t>
+          <t>source_type</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>q_range_max</t>
+          <t>energy_min</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>detector_distance_min</t>
+          <t>energy_max</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>detector_distance_max</t>
+          <t>beam_size_min</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>sample_changer_capacity</t>
+          <t>beam_size_max</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>temperature_control_range</t>
+          <t>flux_density</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>monochromator_type</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>goniometer_type</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>crystal_cooling_capability</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>instrument_code</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>manufacturer</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>installation_date</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>current_status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="K2:K1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="2">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"synchrotron,rotating_anode,microfocus,metal_jet"</formula1>
+    </dataValidation>
+    <dataValidation sqref="N2:N1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"operational,maintenance,offline,commissioning"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1777,57 +2019,57 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>experiment_code</t>
+          <t>q_range_min</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>sample_id</t>
+          <t>q_range_max</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>instrument_id</t>
+          <t>detector_distance_min</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>experiment_date</t>
+          <t>detector_distance_max</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>operator_id</t>
+          <t>sample_changer_capacity</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>technique</t>
+          <t>temperature_control_range</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>experimental_conditions</t>
+          <t>instrument_code</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>data_collection_strategy</t>
+          <t>manufacturer</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>quality_metrics</t>
+          <t>model</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>raw_data_location</t>
+          <t>installation_date</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>processing_status</t>
+          <t>current_status</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
@@ -1847,12 +2089,9 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"cryo_em,xray_crystallography,saxs,waxs,sans,cryo_et,electron_microscopy,mass_spectrometry"</formula1>
-    </dataValidation>
+  <dataValidations count="1">
     <dataValidation sqref="K2:K1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"raw,preprocessing,processing,completed,failed"</formula1>
+      <formula1>"operational,maintenance,offline,commissioning"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1865,85 +2104,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>workflow_code</t>
+          <t>experiment_code</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>workflow_type</t>
+          <t>sample_id</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>experiment_id</t>
+          <t>instrument_id</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>processing_level</t>
+          <t>experiment_date</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>software_name</t>
+          <t>operator_id</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>software_version</t>
+          <t>technique</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>processing_parameters</t>
+          <t>experimental_method</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>compute_resources</t>
+          <t>experimental_conditions</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>started_at</t>
+          <t>data_collection_strategy</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>completed_at</t>
+          <t>quality_metrics</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>output_files</t>
+          <t>raw_data_location</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>processing_status</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>id</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"motion_correction,ctf_estimation,particle_picking,classification_2d,classification_3d,refinement,model_building,phasing,integration,scaling,saxs_analysis,em_2d_classification,mass_spec_deconvolution"</formula1>
+  <dataValidations count="3">
+    <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"cryo_em,xray_crystallography,saxs,waxs,sans,cryo_et,electron_microscopy,mass_spectrometry"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"x_ray_diffraction,neutron_diffraction,electron_diffraction,fiber_diffraction"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"raw,preprocessing,processing,completed,failed"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1956,56 +2206,166 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>file_name</t>
+          <t>workflow_code</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>file_path</t>
+          <t>workflow_type</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>file_format</t>
+          <t>experiment_id</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>file_size_bytes</t>
+          <t>processing_level</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>checksum</t>
+          <t>software_name</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>creation_date</t>
+          <t>software_version</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>data_type</t>
+          <t>additional_software</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>processing_parameters</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>parameters_file_path</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>indexer_module</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>integrator_module</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>scaler_module</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>outlier_rejection_method</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phasing_method</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>search_model_pdb_id</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>tls_used</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ncs_used</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>restraints_other</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ligands_cofactors</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>number_of_waters</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>refinement_resolution_a</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>deposited_to_pdb</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>pdb_id</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>validation_report_path</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>processing_notes</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>compute_resources</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>started_at</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>completed_at</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>output_files</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
           <t>id</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -2013,11 +2373,11 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"mrc,tiff,hdf5,star,pdb,mmcif,mtz,cbf,ascii,thermo_raw,zip"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"micrograph,diffraction,scattering,particles,volume,model,metadata,raw_data,processed_data"</formula1>
+    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"motion_correction,ctf_estimation,particle_picking,classification_2d,classification_3d,refinement,model_building,phasing,integration,scaling,saxs_analysis,em_2d_classification,mass_spec_deconvolution"</formula1>
+    </dataValidation>
+    <dataValidation sqref="N2:N1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"molecular_replacement,sad,mad,sir,mir,siras,miras,fragile_mr"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2041,32 +2401,32 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>acquisition_date</t>
+          <t>file_path</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>pixel_size</t>
+          <t>file_format</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>dimensions_x</t>
+          <t>file_size_bytes</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>dimensions_y</t>
+          <t>checksum</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>exposure_time</t>
+          <t>creation_date</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>dose</t>
+          <t>data_type</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -2086,6 +2446,14 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"mrc,tiff,hdf5,star,pdb,mmcif,mtz,cbf,ascii,thermo_raw,zip"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"micrograph,diffraction,scattering,particles,volume,model,metadata,raw_data,processed_data"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2096,66 +2464,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>defocus</t>
+          <t>file_name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>astigmatism</t>
+          <t>acquisition_date</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>file_name</t>
+          <t>pixel_size</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>acquisition_date</t>
+          <t>dimensions_x</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>pixel_size</t>
+          <t>dimensions_y</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>dimensions_x</t>
+          <t>exposure_time</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>dimensions_y</t>
+          <t>dose</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>exposure_time</t>
+          <t>id</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>dose</t>
+          <t>title</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -2172,71 +2530,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>dimensions_z</t>
+          <t>defocus</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>voxel_size</t>
+          <t>astigmatism</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>reconstruction_method</t>
+          <t>file_name</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>file_name</t>
+          <t>acquisition_date</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>acquisition_date</t>
+          <t>pixel_size</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>pixel_size</t>
+          <t>dimensions_x</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>dimensions_x</t>
+          <t>dimensions_y</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>dimensions_y</t>
+          <t>exposure_time</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>exposure_time</t>
+          <t>dose</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>dose</t>
+          <t>id</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>title</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -2253,91 +2606,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>wavenumber_min</t>
+          <t>dimensions_z</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>wavenumber_max</t>
+          <t>voxel_size</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>spectral_resolution</t>
+          <t>reconstruction_method</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>number_of_scans</t>
+          <t>file_name</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>apodization_function</t>
+          <t>acquisition_date</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>molecular_signatures</t>
+          <t>pixel_size</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>background_correction</t>
+          <t>dimensions_x</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>file_name</t>
+          <t>dimensions_y</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>acquisition_date</t>
+          <t>exposure_time</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>pixel_size</t>
+          <t>dose</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>dimensions_x</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>dimensions_y</t>
+          <t>title</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
-        <is>
-          <t>exposure_time</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>dose</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -2354,111 +2687,91 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U1"/>
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>excitation_wavelength</t>
+          <t>wavenumber_min</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>emission_wavelength</t>
+          <t>wavenumber_max</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>excitation_filter</t>
+          <t>spectral_resolution</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>emission_filter</t>
+          <t>number_of_scans</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>fluorophore</t>
+          <t>apodization_function</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>channel_name</t>
+          <t>molecular_signatures</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>laser_power</t>
+          <t>background_correction</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>pinhole_size</t>
+          <t>file_name</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>quantum_yield</t>
+          <t>acquisition_date</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>defocus</t>
+          <t>pixel_size</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>astigmatism</t>
+          <t>dimensions_x</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>file_name</t>
+          <t>dimensions_y</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>acquisition_date</t>
+          <t>exposure_time</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>pixel_size</t>
+          <t>dose</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>dimensions_x</t>
+          <t>id</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>dimensions_y</t>
+          <t>title</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
-        <is>
-          <t>exposure_time</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>dose</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -2615,107 +2928,117 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:U1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>illumination_type</t>
+          <t>excitation_wavelength</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>magnification</t>
+          <t>emission_wavelength</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>numerical_aperture</t>
+          <t>excitation_filter</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>color_channels</t>
+          <t>emission_filter</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>white_balance</t>
+          <t>fluorophore</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>contrast_method</t>
+          <t>channel_name</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>laser_power</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pinhole_size</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>quantum_yield</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>defocus</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>astigmatism</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>file_name</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>acquisition_date</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>pixel_size</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>dimensions_x</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>dimensions_y</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>exposure_time</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>dose</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"brightfield,darkfield,phase_contrast,dic,fluorescence,confocal,polarized,oblique"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2726,106 +3049,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>beam_energy</t>
+          <t>illumination_type</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>beam_size</t>
+          <t>magnification</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>dwell_time</t>
+          <t>numerical_aperture</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>elements_measured</t>
+          <t>color_channels</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>source_type</t>
+          <t>white_balance</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>detector_type</t>
+          <t>contrast_method</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>flux</t>
+          <t>defocus</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>calibration_standard</t>
+          <t>astigmatism</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>defocus</t>
+          <t>file_name</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>astigmatism</t>
+          <t>acquisition_date</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>file_name</t>
+          <t>pixel_size</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>acquisition_date</t>
+          <t>dimensions_x</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>pixel_size</t>
+          <t>dimensions_y</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>dimensions_x</t>
+          <t>exposure_time</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>dimensions_y</t>
+          <t>dose</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>exposure_time</t>
+          <t>id</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>dose</t>
+          <t>title</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -2833,8 +3146,8 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"synchrotron,rotating_anode,microfocus,metal_jet"</formula1>
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"brightfield,darkfield,phase_contrast,dic,fluorescence,confocal,polarized,oblique"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2847,22 +3160,117 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:T1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>terms</t>
+          <t>beam_energy</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
+        <is>
+          <t>beam_size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>dwell_time</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>elements_measured</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>source_type</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>detector_type</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>flux</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>calibration_standard</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>defocus</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>astigmatism</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>file_name</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>acquisition_date</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>pixel_size</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>dimensions_x</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>dimensions_y</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>exposure_time</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>dose</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"synchrotron,rotating_anode,microfocus,metal_jet"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2873,36 +3281,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>label</t>
+          <t>terms</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
-        <is>
-          <t>definition</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ontology</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -2919,26 +3307,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>sequences</t>
+          <t>label</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>modifications</t>
+          <t>definition</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>ligands</t>
+          <t>ontology</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -2961,17 +3359,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>ph</t>
+          <t>sequences</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>components</t>
+          <t>modifications</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>additives</t>
+          <t>ligands</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -2991,42 +3389,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>temperature</t>
+          <t>ph</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>temperature_unit</t>
+          <t>components</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>additives</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
-        <is>
-          <t>atmosphere</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"celsius,kelvin,fahrenheit"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3037,68 +3425,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>grid_type</t>
+          <t>temperature</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>support_film</t>
+          <t>temperature_unit</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>hole_size</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>vitrification_method</t>
+          <t>atmosphere</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
-        <is>
-          <t>blot_time</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>blot_force</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>humidity_percentage</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>chamber_temperature</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>plasma_treatment</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"c_flat,quantifoil,lacey_carbon,ultrathin_carbon,gold"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"plunge_freezing,high_pressure_freezing,slam_freezing"</formula1>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"celsius,kelvin,fahrenheit"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3111,55 +3471,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>crystallization_method</t>
+          <t>grid_type</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>crystallization_conditions</t>
+          <t>support_film</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>crystal_size</t>
+          <t>hole_size</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>cryoprotectant</t>
+          <t>vitrification_method</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>cryoprotectant_concentration</t>
+          <t>blot_time</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>mounting_method</t>
+          <t>blot_force</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>flash_cooling_method</t>
+          <t>humidity_percentage</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
+        <is>
+          <t>chamber_temperature</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>plasma_treatment</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"vapor_diffusion_hanging,vapor_diffusion_sitting,microbatch,dialysis,free_interface_diffusion"</formula1>
+      <formula1>"c_flat,quantifoil,lacey_carbon,ultrathin_carbon,gold"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"plunge_freezing,high_pressure_freezing,slam_freezing"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3172,42 +3545,137 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:X1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>concentration_series</t>
+          <t>protein_concentration_mg_per_ml</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>buffer_matching_protocol</t>
+          <t>protein_buffer</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>sample_cell_type</t>
+          <t>additives</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>cell_path_length</t>
+          <t>crystallization_method</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>temperature_control</t>
+          <t>screen_name</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
+        <is>
+          <t>temperature_c</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>drop_ratio_protein_to_reservoir</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>drop_volume_nl</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>reservoir_volume_ul</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>seeding_type</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>seed_stock_dilution</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>initial_hit_condition</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>optimization_strategy</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>optimized_condition</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>crystallization_conditions</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>crystal_size_um</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>cryoprotectant</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>cryoprotectant_concentration</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>soak_compound</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>soak_conditions</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>mounting_method</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>flash_cooling_method</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>crystal_notes</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"vapor_diffusion_hanging,vapor_diffusion_sitting,batch,microbatch,lcp,dialysis,free_interface_diffusion"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3310,41 +3778,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>temperature</t>
+          <t>concentration_series</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>humidity</t>
+          <t>buffer_matching_protocol</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>pressure</t>
+          <t>sample_cell_type</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>atmosphere</t>
+          <t>cell_path_length</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>beam_energy</t>
+          <t>temperature_control</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
-        <is>
-          <t>exposure_time</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -3361,47 +3824,47 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>collection_mode</t>
+          <t>temperature</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>total_frames</t>
+          <t>humidity</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>frame_rate</t>
+          <t>pressure</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>total_dose</t>
+          <t>atmosphere</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>dose_per_frame</t>
+          <t>beam_energy</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
+        <is>
+          <t>exposure_time</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"counting,super_resolution,continuous,oscillation,still,batch,sec_saxs,single_particle"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3412,41 +3875,287 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:S1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>collection_mode</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>total_frames</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>frame_rate</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>total_dose</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>dose_per_frame</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>wavelength_a</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>detector</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>detector_distance_mm</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>beam_center_x_px</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>beam_center_y_px</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>beam_size_um</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>flux_photons_per_s</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>transmission_percent</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>attenuator</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>temperature_k</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>oscillation_per_image_deg</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>total_rotation_deg</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>strategy_notes</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"counting,super_resolution,continuous,oscillation,still,batch,sec_saxs,single_particle"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AG1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
           <t>resolution</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>resolution_high_shell_a</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>resolution_low_a</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>completeness</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>completeness_high_res_shell_percent</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>signal_to_noise</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>mean_i_over_sigma_i</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>space_group</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>unit_cell_a</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>unit_cell_b</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>unit_cell_c</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>unit_cell_alpha</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>unit_cell_beta</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>unit_cell_gamma</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>multiplicity</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>cc_half</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>r_merge</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>r_pim</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>wilson_b_factor_a2</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>anomalous_used</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>anom_corr</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>anom_sig_ano</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>r_work</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>r_free</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>ramachandran_favored_percent</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>ramachandran_outliers_percent</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>clashscore</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>molprobity_score</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>average_b_factor_a2</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>i_zero</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>rg</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
         <is>
           <t>r_factor</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>i_zero</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>rg</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -3457,7 +4166,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
